--- a/ig/DM-OCTOBRE-2026/CodeSystem-terminologie-nuva.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-terminologie-nuva.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1144</t>
+    <t>1.0.1164</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T00:00:00+00:00</t>
+    <t>2026-10-01T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1964</t>
+    <t>1996</t>
   </si>
   <si>
     <t>Code</t>

--- a/ig/DM-OCTOBRE-2026/CodeSystem-terminologie-nuva.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-terminologie-nuva.xlsx
@@ -31,10 +31,10 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.3.6.1.4.1.48601.1 (use: usual, )</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-nuva (use: secondary, )</t>
+    <t>OID:1.3.6.1.4.1.48601.1 (use: usual)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/#terminologie-nuva (use: secondary)</t>
   </si>
   <si>
     <t>Version</t>
